--- a/src/main/resources/qm/public/resources/iQSHImportSchema_vi.xlsx
+++ b/src/main/resources/qm/public/resources/iQSHImportSchema_vi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Qcadoo_demo_clone\mes\mes-plugins\fti-plugins-qm\src\main\resources\qm\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91F0FEC-C4E4-496A-B8F3-1ED8D8C6E049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C657CDE0-82B9-4543-830F-DF73E487104B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C3DD0E6-ED60-435A-92B4-4D6BBCAE0B6F}"/>
   </bookViews>
@@ -38,15 +38,23 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>Mã số sản phẩm</t>
+    <t>Mã sản phẩm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -74,8 +82,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,11 +424,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>

--- a/src/main/resources/qm/public/resources/iQSHImportSchema_vi.xlsx
+++ b/src/main/resources/qm/public/resources/iQSHImportSchema_vi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Qcadoo_demo_clone\mes\mes-plugins\fti-plugins-qm\src\main\resources\qm\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C657CDE0-82B9-4543-830F-DF73E487104B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CA6CA7-25A3-4C63-962E-348065A0E0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C3DD0E6-ED60-435A-92B4-4D6BBCAE0B6F}"/>
   </bookViews>
